--- a/excels/Cronograma_DDRISS_Final.xlsx
+++ b/excels/Cronograma_DDRISS_Final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kennethram\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni\OCTAVO SEMESTRE\Redaccion\PropuestaProyectoDeCarrera\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA123713-C570-46B1-9302-8A4DED602478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1C206D-928F-4D52-AE12-FBB19D31C95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,6 @@
     <sheet name="Cronograma" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -111,9 +106,6 @@
     <t>27–30 nov</t>
   </si>
   <si>
-    <t>FASE INICIAL: visita, investigación y levantamiento de requerimientos</t>
-  </si>
-  <si>
     <t>Todos</t>
   </si>
   <si>
@@ -183,12 +175,6 @@
     <t>Diseñar flujo de estados e interfaces de revisión, corrección, aprobación y cierre</t>
   </si>
   <si>
-    <t>Implementar resultados de validación y control de estados del reporte</t>
-  </si>
-  <si>
-    <t>Implementar envío, revisión, corrección, aprobación, cierre y rectificación</t>
-  </si>
-  <si>
     <t>Integrar el registro automático de trazabilidad asociado al flujo</t>
   </si>
   <si>
@@ -240,9 +226,6 @@
     <t>Verificar permisos, roles y controles básicos de acceso</t>
   </si>
   <si>
-    <t>Realizar pruebas con usuarios y recopilar retroalimentación</t>
-  </si>
-  <si>
     <t>Analizar observaciones y realizar ajustes finales</t>
   </si>
   <si>
@@ -265,6 +248,18 @@
   </si>
   <si>
     <t>Referencia Scrum: https://scrumguides.org/scrum-guide.html | Criterios de organización ajustados conforme a la asesoría técnica del 23 de septiembre de 2026.</t>
+  </si>
+  <si>
+    <t>FASE INICIAL: visita, investigación y levantamiento de requerimientos iniciales</t>
+  </si>
+  <si>
+    <t>Desarrollar envío, revisión, corrección, aprobación, cierre y rectificación</t>
+  </si>
+  <si>
+    <t>Desarrollar resultados de validación y control de estados del reporte</t>
+  </si>
+  <si>
+    <t>Realizar pruebas alfa con usuarios y recopilar retroalimentación</t>
   </si>
 </sst>
 </file>
@@ -441,91 +436,91 @@
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -892,7 +887,7 @@
     </row>
     <row r="6" spans="1:15" ht="17.55" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="B6" s="9">
         <v>46241</v>
@@ -912,12 +907,12 @@
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="16.05" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="13">
         <v>46241</v>
@@ -937,12 +932,12 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.05" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="13">
         <v>46241</v>
@@ -962,12 +957,12 @@
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.05" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="13">
         <v>46242</v>
@@ -987,12 +982,12 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="27.6" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="13">
         <v>46243</v>
@@ -1012,12 +1007,12 @@
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="31.8" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="13">
         <v>46244</v>
@@ -1037,12 +1032,12 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="28.8" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="9">
         <v>46289</v>
@@ -1062,12 +1057,12 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="19.2" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46289</v>
@@ -1087,12 +1082,12 @@
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="24" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="13">
         <v>46289</v>
@@ -1112,12 +1107,12 @@
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="19.2" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="13">
         <v>46290</v>
@@ -1137,12 +1132,12 @@
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="18.600000000000001" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="13">
         <v>46291</v>
@@ -1162,12 +1157,12 @@
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="21.6" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="13">
         <v>46293</v>
@@ -1187,12 +1182,12 @@
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="19.8" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="13">
         <v>46294</v>
@@ -1212,12 +1207,12 @@
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="13">
         <v>46289</v>
@@ -1237,12 +1232,12 @@
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
       <c r="O19" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.05" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="18">
         <v>46298</v>
@@ -1262,12 +1257,12 @@
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
       <c r="O20" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="16.05" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="9">
         <v>46299</v>
@@ -1287,12 +1282,12 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="17.55" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="13">
         <v>46299</v>
@@ -1312,12 +1307,12 @@
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="25.8" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="13">
         <v>46299</v>
@@ -1337,12 +1332,12 @@
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="16.05" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="13">
         <v>46300</v>
@@ -1362,12 +1357,12 @@
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="16.05" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="13">
         <v>46301</v>
@@ -1387,12 +1382,12 @@
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="16.05" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="13">
         <v>46303</v>
@@ -1412,12 +1407,12 @@
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="16.05" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="13">
         <v>46304</v>
@@ -1437,12 +1432,12 @@
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="16.05" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="13">
         <v>46299</v>
@@ -1462,12 +1457,12 @@
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="16.05" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="13">
         <v>46308</v>
@@ -1487,12 +1482,12 @@
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="16.05" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="9">
         <v>46309</v>
@@ -1512,12 +1507,12 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
       <c r="O30" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="29.4" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="18">
         <v>46309</v>
@@ -1537,12 +1532,12 @@
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
       <c r="O31" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="31.8" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" s="13">
         <v>46309</v>
@@ -1562,12 +1557,12 @@
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
       <c r="O32" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="21.6" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13">
         <v>46310</v>
@@ -1587,12 +1582,12 @@
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="16.05" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B34" s="13">
         <v>46311</v>
@@ -1612,12 +1607,12 @@
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
       <c r="O34" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="16.05" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B35" s="13">
         <v>46313</v>
@@ -1637,12 +1632,12 @@
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
       <c r="O35" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="16.05" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B36" s="13">
         <v>46315</v>
@@ -1662,12 +1657,12 @@
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
       <c r="O36" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="16.05" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="13">
         <v>46314</v>
@@ -1687,12 +1682,12 @@
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="16.05" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="13">
         <v>46309</v>
@@ -1712,12 +1707,12 @@
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="16.05" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="13">
         <v>46318</v>
@@ -1737,12 +1732,12 @@
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="16.05" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B40" s="9">
         <v>46319</v>
@@ -1762,12 +1757,12 @@
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
       <c r="O40" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="17.55" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" s="13">
         <v>46319</v>
@@ -1787,12 +1782,12 @@
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
       <c r="O41" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="16.05" customHeight="1">
       <c r="A42" s="12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B42" s="13">
         <v>46319</v>
@@ -1812,12 +1807,12 @@
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
       <c r="O42" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="16.05" customHeight="1">
       <c r="A43" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B43" s="13">
         <v>46320</v>
@@ -1837,12 +1832,12 @@
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
       <c r="O43" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="16.05" customHeight="1">
       <c r="A44" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B44" s="13">
         <v>46321</v>
@@ -1862,12 +1857,12 @@
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
       <c r="O44" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="16.05" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B45" s="13">
         <v>46323</v>
@@ -1887,12 +1882,12 @@
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
       <c r="O45" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="16.05" customHeight="1">
       <c r="A46" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="13">
         <v>46324</v>
@@ -1912,12 +1907,12 @@
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
       <c r="O46" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="16.05" customHeight="1">
       <c r="A47" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="13">
         <v>46319</v>
@@ -1937,12 +1932,12 @@
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
       <c r="O47" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="16.05" customHeight="1">
       <c r="A48" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="13">
         <v>46328</v>
@@ -1962,12 +1957,12 @@
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
       <c r="O48" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="16.05" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B49" s="9">
         <v>46329</v>
@@ -1987,12 +1982,12 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
       <c r="O49" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="17.55" customHeight="1">
       <c r="A50" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" s="13">
         <v>46329</v>
@@ -2012,12 +2007,12 @@
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
       <c r="O50" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="16.05" customHeight="1">
       <c r="A51" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B51" s="13">
         <v>46329</v>
@@ -2037,12 +2032,12 @@
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
       <c r="O51" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="16.05" customHeight="1">
       <c r="A52" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B52" s="13">
         <v>46330</v>
@@ -2062,12 +2057,12 @@
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
       <c r="O52" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="16.05" customHeight="1">
       <c r="A53" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B53" s="13">
         <v>46331</v>
@@ -2087,12 +2082,12 @@
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
       <c r="O53" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="16.05" customHeight="1">
       <c r="A54" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B54" s="13">
         <v>46333</v>
@@ -2112,12 +2107,12 @@
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
       <c r="O54" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="16.05" customHeight="1">
       <c r="A55" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B55" s="13">
         <v>46334</v>
@@ -2137,12 +2132,12 @@
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
       <c r="O55" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="16.05" customHeight="1">
       <c r="A56" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="13">
         <v>46335</v>
@@ -2162,12 +2157,12 @@
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
       <c r="O56" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="16.05" customHeight="1">
       <c r="A57" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="13">
         <v>46329</v>
@@ -2187,12 +2182,12 @@
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
       <c r="O57" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="16.05" customHeight="1">
       <c r="A58" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="13">
         <v>46338</v>
@@ -2212,12 +2207,12 @@
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
       <c r="O58" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="16.05" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B59" s="9">
         <v>46339</v>
@@ -2237,12 +2232,12 @@
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
       <c r="O59" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="17.55" customHeight="1">
       <c r="A60" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B60" s="13">
         <v>46339</v>
@@ -2262,12 +2257,12 @@
       <c r="M60" s="15"/>
       <c r="N60" s="15"/>
       <c r="O60" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="16.05" customHeight="1">
       <c r="A61" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B61" s="13">
         <v>46340</v>
@@ -2287,12 +2282,12 @@
       <c r="M61" s="15"/>
       <c r="N61" s="15"/>
       <c r="O61" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="16.05" customHeight="1">
       <c r="A62" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B62" s="13">
         <v>46342</v>
@@ -2312,12 +2307,12 @@
       <c r="M62" s="15"/>
       <c r="N62" s="15"/>
       <c r="O62" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="16.05" customHeight="1">
       <c r="A63" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B63" s="13">
         <v>46342</v>
@@ -2337,12 +2332,12 @@
       <c r="M63" s="15"/>
       <c r="N63" s="15"/>
       <c r="O63" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="16.05" customHeight="1">
       <c r="A64" s="12" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B64" s="13">
         <v>46344</v>
@@ -2362,12 +2357,12 @@
       <c r="M64" s="14"/>
       <c r="N64" s="15"/>
       <c r="O64" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="16.05" customHeight="1">
       <c r="A65" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B65" s="13">
         <v>46346</v>
@@ -2387,12 +2382,12 @@
       <c r="M65" s="14"/>
       <c r="N65" s="15"/>
       <c r="O65" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="16.05" customHeight="1">
       <c r="A66" s="12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B66" s="13">
         <v>46344</v>
@@ -2412,12 +2407,12 @@
       <c r="M66" s="14"/>
       <c r="N66" s="15"/>
       <c r="O66" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="16.05" customHeight="1">
       <c r="A67" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B67" s="13">
         <v>46350</v>
@@ -2437,12 +2432,12 @@
       <c r="M67" s="14"/>
       <c r="N67" s="15"/>
       <c r="O67" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="16.05" customHeight="1">
       <c r="A68" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B68" s="13">
         <v>46351</v>
@@ -2462,12 +2457,12 @@
       <c r="M68" s="14"/>
       <c r="N68" s="15"/>
       <c r="O68" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="16.05" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B69" s="13">
         <v>46353</v>
@@ -2487,12 +2482,12 @@
       <c r="M69" s="15"/>
       <c r="N69" s="14"/>
       <c r="O69" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="16.05" customHeight="1">
       <c r="A70" s="22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B70" s="23">
         <v>46355</v>
@@ -2512,7 +2507,7 @@
       <c r="M70" s="25"/>
       <c r="N70" s="26"/>
       <c r="O70" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="16.05" customHeight="1">
@@ -2534,7 +2529,7 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B72" s="29"/>
       <c r="C72" s="29"/>
@@ -2553,7 +2548,7 @@
     </row>
     <row r="73" spans="1:15" ht="22.35" customHeight="1">
       <c r="A73" s="29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B73" s="29"/>
       <c r="C73" s="29"/>
